--- a/survey_templates/041_hotel_recommendation_form--survey_templates.xlsx
+++ b/survey_templates/041_hotel_recommendation_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,115 +515,131 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>travel_date</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Travel Date</t>
+          <t>What is your name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>budget</t>
+          <t>travel_date</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>budget</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Travel Date</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>mm/dd/yyyy</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>budget</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>prophets_location</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please enter your budget</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hotel_rating</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hotel_rating</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select all that apply</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>prophets_location</t>
+          <t>hotel_rating</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Prophets Location</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Hotel Rating</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Select a rating</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,13 +656,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>travel_length</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Travel Length</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Select a duration</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,59 +683,71 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>travel_agent</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Travel Agent</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Are you a travel agent?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>prophets_length</t>
+          <t>preferred_hotel</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Prophets Length</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Preferred Hotel</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select all that apply</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>preferred_hotel</t>
+          <t>travel_mode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>preferred_hotel</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Travel Mode</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>How do you plan to travel?</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,35 +759,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>travel_mode</t>
+          <t>prophets_length</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>travel_mode</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Prophets Length</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Select a duration</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>travel_mode</t>
+          <t>prophets_location</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>travel_mode</t>
+          <t>Prophets Location</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,18 +809,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>budget</t>
+          <t>prophets_budget</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>prophets_budget</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Prophets Budget</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please enter your budget</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,18 +836,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>travel_date</t>
+          <t>travel_date_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>prophets_travel_date</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Travel Date 2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>mm/dd/yyyy</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,41 +863,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>preferred_hotel</t>
+          <t>preferred_hotel_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>preferred_hotel</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Preferred Hotel 2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Select all that apply</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>travel_agent</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>travel_agent</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -868,12 +893,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +926,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>City</t>
         </is>
       </c>
     </row>
@@ -918,12 +943,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>country</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Country</t>
         </is>
       </c>
     </row>
@@ -935,12 +960,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>region</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Region</t>
         </is>
       </c>
     </row>
@@ -952,12 +977,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -969,12 +994,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -986,199 +1011,199 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>prophets_location_choices</t>
+          <t>travel_length_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>1-3_days</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>1-3 days</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>prophets_location_choices</t>
+          <t>travel_length_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>1-7_days</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>1-7 days</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>prophets_location_choices</t>
+          <t>travel_length_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>more_than_7_days</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>More than 7 days</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>travel_length_choices</t>
+          <t>travel_agent_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>travel_length_choices</t>
+          <t>travel_agent_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option11</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option11</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>travel_length_choices</t>
+          <t>preferred_hotel_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option12</t>
+          <t>luxury</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option12</t>
+          <t>Luxury</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>travel_agent_choices</t>
+          <t>preferred_hotel_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option13</t>
+          <t>budget</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option13</t>
+          <t>Budget</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>travel_agent_choices</t>
+          <t>preferred_hotel_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option14</t>
+          <t>boutique</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option14</t>
+          <t>Boutique</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>travel_agent_choices</t>
+          <t>travel_mode_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option15</t>
+          <t>flight</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option15</t>
+          <t>Flight</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>prophets_length_choices</t>
+          <t>travel_mode_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option16</t>
+          <t>train</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option16</t>
+          <t>Train</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>prophets_length_choices</t>
+          <t>travel_mode_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option17</t>
+          <t>car</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option17</t>
+          <t>Car</t>
         </is>
       </c>
     </row>
@@ -1190,267 +1215,148 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option18</t>
+          <t>1-3_days</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option18</t>
+          <t>1-3 days</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>preferred_hotel_choices</t>
+          <t>prophets_length_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option19</t>
+          <t>1-7_days</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option19</t>
+          <t>1-7 days</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>preferred_hotel_choices</t>
+          <t>prophets_length_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option20</t>
+          <t>more_than_7_days</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option20</t>
+          <t>More than 7 days</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>preferred_hotel_choices</t>
+          <t>prophets_location_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option21</t>
+          <t>beach</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option21</t>
+          <t>Beach</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>travel_mode_choices</t>
+          <t>prophets_location_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option22</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option22</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>travel_mode_choices</t>
+          <t>prophets_location_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option23</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option23</t>
+          <t>City</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>travel_mode_choices</t>
+          <t>preferred_hotel_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option24</t>
+          <t>luxury</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option24</t>
+          <t>Luxury</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>travel_mode_choices</t>
+          <t>preferred_hotel_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option25</t>
+          <t>budget</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option25</t>
+          <t>Budget</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>travel_mode_choices</t>
+          <t>preferred_hotel_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option26</t>
+          <t>boutique</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option26</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>travel_mode_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>option27</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>option27</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>preferred_hotel_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>option28</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>option28</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>preferred_hotel_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>option29</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>option29</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>preferred_hotel_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>option30</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>option30</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>travel_agent_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>option31</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>option31</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>travel_agent_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>option32</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>option32</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>travel_agent_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>option33</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>option33</t>
+          <t>Boutique</t>
         </is>
       </c>
     </row>
